--- a/CYP1A2/CYP1A2_Allele_def_rs_excluidos.xlsx
+++ b/CYP1A2/CYP1A2_Allele_def_rs_excluidos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP1A2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="110">
   <si>
     <t>rsID</t>
   </si>
@@ -341,6 +341,15 @@
   </si>
   <si>
     <t>rs/*alelo</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2505559894 (CYP1A2_Haplotypes-PS216394-1454147960)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dbSNP </t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2505559894</t>
   </si>
 </sst>
 </file>
@@ -372,7 +381,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -391,6 +400,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -405,7 +420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -415,6 +430,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1191,13 +1207,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="28" max="28" width="11.140625" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1276,22 +1292,22 @@
       <c r="Z1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1368,7 +1384,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1378,17 +1394,17 @@
       <c r="Z4" t="s">
         <v>12</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>0</v>
       </c>
-      <c r="AB4" t="s">
-        <v>104</v>
-      </c>
       <c r="AC4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD4" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -1398,8 +1414,20 @@
       <c r="Z5" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AA5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -1409,17 +1437,17 @@
       <c r="Z6" t="s">
         <v>2</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>8.2949999999999997E-5</v>
       </c>
-      <c r="AB6" t="s">
-        <v>104</v>
-      </c>
       <c r="AC6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -1429,17 +1457,17 @@
       <c r="Z7" t="s">
         <v>4</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>0</v>
       </c>
-      <c r="AB7" t="s">
-        <v>104</v>
-      </c>
       <c r="AC7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1449,17 +1477,17 @@
       <c r="Z8" t="s">
         <v>17</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>1.3560000000000001E-5</v>
       </c>
-      <c r="AB8" t="s">
-        <v>104</v>
-      </c>
       <c r="AC8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1469,17 +1497,17 @@
       <c r="Z9" t="s">
         <v>10</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>1.6950000000000001E-6</v>
       </c>
-      <c r="AB9" t="s">
-        <v>104</v>
-      </c>
       <c r="AC9" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -1489,17 +1517,17 @@
       <c r="Z10" t="s">
         <v>3</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>0</v>
       </c>
-      <c r="AB10" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC10" s="2" t="s">
+      <c r="AC10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD10" s="2" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>58</v>
       </c>
@@ -1509,17 +1537,17 @@
       <c r="Z11" t="s">
         <v>1</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>4.5970000000000002E-5</v>
       </c>
-      <c r="AB11" t="s">
-        <v>104</v>
-      </c>
       <c r="AC11" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD11" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -1529,17 +1557,17 @@
       <c r="Z12" t="s">
         <v>23</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>1.9490000000000001E-5</v>
       </c>
-      <c r="AB12" t="s">
-        <v>104</v>
-      </c>
       <c r="AC12" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1549,17 +1577,17 @@
       <c r="Z13" t="s">
         <v>18</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>1.102E-5</v>
       </c>
-      <c r="AB13" t="s">
-        <v>104</v>
-      </c>
       <c r="AC13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>62</v>
       </c>
@@ -1569,17 +1597,17 @@
       <c r="Z14" t="s">
         <v>11</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>9.3219999999999999E-6</v>
       </c>
-      <c r="AB14" t="s">
-        <v>104</v>
-      </c>
       <c r="AC14" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -1589,17 +1617,17 @@
       <c r="Z15" t="s">
         <v>5</v>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <v>2.7209999999999999E-5</v>
       </c>
-      <c r="AB15" t="s">
-        <v>104</v>
-      </c>
       <c r="AC15" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD15" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>66</v>
       </c>
@@ -1609,17 +1637,17 @@
       <c r="Z16" t="s">
         <v>6</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <v>4.6529999999999998E-4</v>
       </c>
-      <c r="AB16" t="s">
-        <v>104</v>
-      </c>
       <c r="AC16" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD16" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -1629,17 +1657,17 @@
       <c r="Z17" t="s">
         <v>9</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>8.1950000000000002E-4</v>
       </c>
-      <c r="AB17" t="s">
-        <v>104</v>
-      </c>
       <c r="AC17" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -1649,17 +1677,17 @@
       <c r="Z18" t="s">
         <v>7</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>3.7289999999999997E-5</v>
       </c>
-      <c r="AB18" t="s">
-        <v>104</v>
-      </c>
       <c r="AC18" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD18" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -1669,17 +1697,17 @@
       <c r="Z19" t="s">
         <v>16</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>0</v>
       </c>
-      <c r="AB19" t="s">
-        <v>104</v>
-      </c>
       <c r="AC19" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD19" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -1689,17 +1717,17 @@
       <c r="Z20" t="s">
         <v>21</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>4.2370000000000003E-6</v>
       </c>
-      <c r="AB20" t="s">
-        <v>104</v>
-      </c>
       <c r="AC20" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD20" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>71</v>
       </c>
@@ -1709,17 +1737,17 @@
       <c r="Z21" t="s">
         <v>13</v>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <v>2.9920000000000001E-4</v>
       </c>
-      <c r="AB21" t="s">
-        <v>104</v>
-      </c>
       <c r="AC21" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD21" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>72</v>
       </c>
@@ -1729,17 +1757,17 @@
       <c r="Z22" t="s">
         <v>15</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>0</v>
       </c>
-      <c r="AB22" t="s">
-        <v>104</v>
-      </c>
       <c r="AC22" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD22" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -1749,17 +1777,17 @@
       <c r="Z23" t="s">
         <v>20</v>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <v>0</v>
       </c>
-      <c r="AB23" t="s">
-        <v>104</v>
-      </c>
       <c r="AC23" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD23" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -1769,17 +1797,17 @@
       <c r="Z24" t="s">
         <v>22</v>
       </c>
-      <c r="AA24">
+      <c r="AB24">
         <v>0</v>
       </c>
-      <c r="AB24" t="s">
-        <v>104</v>
-      </c>
       <c r="AC24" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD24" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -1789,17 +1817,17 @@
       <c r="Z25" t="s">
         <v>24</v>
       </c>
-      <c r="AA25">
+      <c r="AB25">
         <v>1.697E-6</v>
       </c>
-      <c r="AB25" t="s">
-        <v>104</v>
-      </c>
       <c r="AC25" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>76</v>
       </c>
@@ -1809,17 +1837,17 @@
       <c r="Z26" t="s">
         <v>8</v>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <v>2.2030000000000001E-5</v>
       </c>
-      <c r="AB26" t="s">
-        <v>104</v>
-      </c>
       <c r="AC26" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD26" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>77</v>
       </c>
@@ -1829,28 +1857,28 @@
       <c r="Z27" t="s">
         <v>14</v>
       </c>
-      <c r="AA27">
+      <c r="AB27">
         <v>1.6950000000000001E-6</v>
       </c>
-      <c r="AB27" t="s">
-        <v>104</v>
-      </c>
       <c r="AC27" t="s">
+        <v>104</v>
+      </c>
+      <c r="AD27" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="Z28" t="s">
         <v>103</v>
       </c>
-      <c r="AA28">
-        <f>SUM(AA4:AA27)*100</f>
+      <c r="AB28">
+        <f>SUM(AB4:AB27)*100</f>
         <v>0.18621659999999998</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AC10" r:id="rId1"/>
+    <hyperlink ref="AD10" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CYP1A2/CYP1A2_Allele_def_rs_excluidos.xlsx
+++ b/CYP1A2/CYP1A2_Allele_def_rs_excluidos.xlsx
@@ -1872,7 +1872,6 @@
         <v>103</v>
       </c>
       <c r="AB28">
-        <f>SUM(AB4:AB27)*100</f>
         <v>0.18621659999999998</v>
       </c>
     </row>
